--- a/global/rates.xlsx
+++ b/global/rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7108,6 +7108,484 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HAPAG</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>3252</v>
+      </c>
+      <c r="J118" t="n">
+        <v>355</v>
+      </c>
+      <c r="K118" t="n">
+        <v>165</v>
+      </c>
+      <c r="L118" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4001.7</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Quick Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HAPAG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>3252</v>
+      </c>
+      <c r="J119" t="n">
+        <v>355</v>
+      </c>
+      <c r="K119" t="n">
+        <v>165</v>
+      </c>
+      <c r="L119" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="M119" t="n">
+        <v>4001.7</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Quick Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HAPAG</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>3252</v>
+      </c>
+      <c r="J120" t="n">
+        <v>355</v>
+      </c>
+      <c r="K120" t="n">
+        <v>165</v>
+      </c>
+      <c r="L120" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4001.7</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Quick Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HAPAG</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>3252</v>
+      </c>
+      <c r="J121" t="n">
+        <v>355</v>
+      </c>
+      <c r="K121" t="n">
+        <v>165</v>
+      </c>
+      <c r="L121" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4001.7</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Quick Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CMACGM</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ICONTAINERS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>31-May-2026</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J124" t="n">
+        <v>629</v>
+      </c>
+      <c r="K124" t="n">
+        <v>219</v>
+      </c>
+      <c r="L124" t="n">
+        <v>214</v>
+      </c>
+      <c r="M124" t="n">
+        <v>2362</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J125" t="n">
+        <v>602</v>
+      </c>
+      <c r="K125" t="n">
+        <v>219</v>
+      </c>
+      <c r="L125" t="n">
+        <v>217.1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2338.1</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GEORGETOWN, GY</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1 × 20' ST</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
